--- a/quizzes/033_photoelectric_effect_quiz--quizzes.xlsx
+++ b/quizzes/033_photoelectric_effect_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Quiz Completed Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is the type of radiation</t>
+          <t>Question6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What is the type of radiation</t>
+          <t>Question7</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What is the type of radiation</t>
+          <t>Question9</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>What is the type of detector</t>
+          <t>Question10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>What is the type of radiation</t>
+          <t>Question11</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1199,401 +1199,350 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>photoelectric_effect_quiz_score_choices</t>
+          <t>quiz_completed_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>photoelectric_effect_quiz_score_choices</t>
+          <t>quiz_completed_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>photoelectric_effect_quiz_score_choices</t>
+          <t>quiz_start2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>continue</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Continue</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quiz_completed_choices</t>
+          <t>quiz_start2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quiz_completed_choices</t>
+          <t>question4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>beta_rays</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Beta Rays</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quiz_start2_choices</t>
+          <t>question4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>gamma_rays</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Continue</t>
+          <t>Gamma Rays</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>quiz_start2_choices</t>
+          <t>question5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>deflection</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Deflection</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question4_choices</t>
+          <t>question5_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>beta_rays</t>
+          <t>scattering</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Beta Rays</t>
+          <t>Scattering</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question4_choices</t>
+          <t>question6_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gamma_rays</t>
+          <t>x-rays</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gamma Rays</t>
+          <t>X-Rays</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question5_choices</t>
+          <t>question6_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>deflection</t>
+          <t>neutrons</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Deflection</t>
+          <t>Neutrons</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question5_choices</t>
+          <t>question7_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>scattering</t>
+          <t>protons</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scattering</t>
+          <t>Protons</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question6_choices</t>
+          <t>question7_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>x-rays</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>X-Rays</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question6_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>neutrons</t>
+          <t>scintillator</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Neutrons</t>
+          <t>Scintillator</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question7_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>protons</t>
+          <t>phosphor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Protons</t>
+          <t>Phosphor</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question7_choices</t>
+          <t>question9_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>electron_rays</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Electron Rays</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question8_choices</t>
+          <t>question9_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>scintillator</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scintillator</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question8_choices</t>
+          <t>question10_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>phosphor</t>
+          <t>ionisation_chamber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phosphor</t>
+          <t>Ionisation Chamber</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question9_choices</t>
+          <t>question10_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>electron_rays</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Electron Rays</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question9_choices</t>
+          <t>question11_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>neutrons</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Neutrons</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question10_choices</t>
+          <t>question11_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ionisation_chamber</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
-        <is>
-          <t>Ionisation Chamber</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>question10_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>question11_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>neutrons</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Neutrons</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>question11_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
